--- a/FontSubset.xlsx
+++ b/FontSubset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kage\Documents\GitHub\Sculpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E7AE35-64D0-4226-8CDC-93B22DBF7084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD022A6E-B1C2-4737-962B-293EF974B061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -215,9 +215,6 @@
     <t>Crit</t>
   </si>
   <si>
-    <t>&lt;center&gt;Critical Options&lt;/center&gt;</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Omen:&lt;/b&gt; inflict the &lt;b&gt;Cursed&lt;/b&gt; status effect.</t>
   </si>
   <si>
@@ -349,6 +346,9 @@
   </si>
   <si>
     <t>At the start of your turn, each storm cloud grows by one hex in all directions.</t>
+  </si>
+  <si>
+    <t>Critical Options</t>
   </si>
 </sst>
 </file>
@@ -470,7 +470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -527,49 +527,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB4C6E7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF6B0DD"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill>
@@ -783,7 +745,7 @@
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Effect 2 Y"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Effect 2 Type"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Effect 2 Title"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Effect 2" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Effect 2" dataDxfId="15"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name=".2"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Effect 3 Y"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Effect 3 Type"/>
@@ -1023,7 +985,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -1038,7 +1000,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>7</v>
@@ -1053,7 +1015,7 @@
         <v>10</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>11</v>
@@ -1068,7 +1030,7 @@
         <v>14</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>15</v>
@@ -1128,8 +1090,8 @@
       <c r="F2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="20" t="s">
-        <v>84</v>
+      <c r="G2" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>33</v>
@@ -1220,11 +1182,11 @@
       <c r="F3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>85</v>
+      <c r="G3" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="6">
@@ -1234,7 +1196,7 @@
         <v>30</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M3" s="6" t="s">
         <v>37</v>
@@ -1246,11 +1208,11 @@
       <c r="P3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="20" t="s">
-        <v>80</v>
+      <c r="Q3" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S3" s="7"/>
       <c r="T3" s="6"/>
@@ -1311,10 +1273,10 @@
         <v>30</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="6"/>
@@ -1385,7 +1347,7 @@
         <v>30</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>42</v>
@@ -1398,7 +1360,7 @@
         <v>30</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
@@ -1467,7 +1429,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>45</v>
@@ -1480,7 +1442,7 @@
         <v>40</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>46</v>
@@ -1493,7 +1455,7 @@
         <v>31</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>47</v>
@@ -1583,10 +1545,10 @@
         <v>55</v>
       </c>
       <c r="Q7" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="R7" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="S7" s="7"/>
       <c r="T7" s="6"/>
@@ -1633,7 +1595,7 @@
     </row>
     <row r="8" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>49</v>
@@ -1647,10 +1609,10 @@
         <v>52</v>
       </c>
       <c r="G8" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>61</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="8">
@@ -1660,10 +1622,10 @@
         <v>31</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N8" s="14"/>
       <c r="O8" s="6">
@@ -1673,10 +1635,10 @@
         <v>55</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S8" s="7"/>
       <c r="T8" s="6"/>
@@ -1723,7 +1685,7 @@
     </row>
     <row r="9" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>49</v>
@@ -1737,10 +1699,10 @@
         <v>52</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="6">
@@ -1750,10 +1712,10 @@
         <v>30</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N9" s="14"/>
       <c r="O9" s="6">
@@ -1763,10 +1725,10 @@
         <v>55</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S9" s="7"/>
       <c r="T9" s="6"/>
@@ -1813,7 +1775,7 @@
     </row>
     <row r="10" spans="1:33" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>49</v>
@@ -1827,10 +1789,10 @@
         <v>31</v>
       </c>
       <c r="G10" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="6">
@@ -1840,10 +1802,10 @@
         <v>30</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N10" s="14"/>
       <c r="O10" s="6">
@@ -1853,10 +1815,10 @@
         <v>30</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S10" s="7"/>
       <c r="T10" s="6"/>
@@ -4778,36 +4740,36 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:C1 J1:M1 O1:R1 T1:AG1 B2:B8">
-    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="Accessory">
+    <cfRule type="containsText" dxfId="14" priority="17" operator="containsText" text="Accessory">
       <formula>NOT(ISERROR(SEARCH("Accessory",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="Armour">
+    <cfRule type="containsText" dxfId="13" priority="18" operator="containsText" text="Armour">
       <formula>NOT(ISERROR(SEARCH("Armour",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="Equipment">
+    <cfRule type="containsText" dxfId="12" priority="19" operator="containsText" text="Equipment">
       <formula>NOT(ISERROR(SEARCH("Equipment",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="20" operator="containsText" text="Impression">
+    <cfRule type="containsText" dxfId="11" priority="20" operator="containsText" text="Impression">
       <formula>NOT(ISERROR(SEARCH("Impression",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="21" operator="containsText" text="Spell">
+    <cfRule type="containsText" dxfId="10" priority="21" operator="containsText" text="Spell">
       <formula>NOT(ISERROR(SEARCH("Spell",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:B89">
-    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="Accessory">
+    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="Accessory">
       <formula>NOT(ISERROR(SEARCH("Accessory",B11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="Armour">
+    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Armour">
       <formula>NOT(ISERROR(SEARCH("Armour",B11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="9" operator="containsText" text="Equipment">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="Equipment">
       <formula>NOT(ISERROR(SEARCH("Equipment",B11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="Impression">
+    <cfRule type="containsText" dxfId="6" priority="10" operator="containsText" text="Impression">
       <formula>NOT(ISERROR(SEARCH("Impression",B11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="Spell">
+    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="Spell">
       <formula>NOT(ISERROR(SEARCH("Spell",B11)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/FontSubset.xlsx
+++ b/FontSubset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kage\Documents\GitHub\Sculpt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD022A6E-B1C2-4737-962B-293EF974B061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57819DEC-2343-43D9-9E5D-5774540C561A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
